--- a/Data/FlightPlan/FPL_23SEP26.xlsx
+++ b/Data/FlightPlan/FPL_23SEP26.xlsx
@@ -596,6 +596,9 @@
     <t>DPS</t>
   </si>
   <si>
+    <t>13:41</t>
+  </si>
+  <si>
     <t>17:25</t>
   </si>
   <si>
@@ -899,6 +902,9 @@
     <t>VN-A637</t>
   </si>
   <si>
+    <t>10:58</t>
+  </si>
+  <si>
     <t>431A *</t>
   </si>
   <si>
@@ -944,6 +950,9 @@
     <t>11:15</t>
   </si>
   <si>
+    <t>11:04</t>
+  </si>
+  <si>
     <t>22:05</t>
   </si>
   <si>
@@ -1058,6 +1067,9 @@
     <t>VN-A653</t>
   </si>
   <si>
+    <t>09:53</t>
+  </si>
+  <si>
     <t>VN-A656</t>
   </si>
   <si>
@@ -1070,7 +1082,7 @@
     <t>07:43</t>
   </si>
   <si>
-    <t>15:48</t>
+    <t>15:43</t>
   </si>
   <si>
     <t>FSZ</t>
@@ -1091,6 +1103,9 @@
     <t>06:05</t>
   </si>
   <si>
+    <t>10:54</t>
+  </si>
+  <si>
     <t>VN-A661</t>
   </si>
   <si>
@@ -1193,7 +1208,7 @@
     <t>04:05</t>
   </si>
   <si>
-    <t>09:48</t>
+    <t>09:49</t>
   </si>
   <si>
     <t>VN-A677</t>
@@ -1298,6 +1313,9 @@
     <t>07:09</t>
   </si>
   <si>
+    <t>09:58</t>
+  </si>
+  <si>
     <t>19:35</t>
   </si>
   <si>
@@ -1322,7 +1340,7 @@
     <t>Total Record(s): 360</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 23, 2026 08:48</t>
+    <t xml:space="preserve">Generated on  Sep 23, 2026 09:01</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4976,7 +4994,9 @@
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
-      <c r="M109" s="7"/>
+      <c t="s" r="M109" s="7">
+        <v>195</v>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c t="s" r="A110" s="6">
@@ -5005,7 +5025,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5032,13 +5052,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="I111" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5062,7 +5082,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>44</v>
@@ -5071,7 +5091,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5104,7 +5124,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5122,11 +5142,11 @@
         <v>153</v>
       </c>
       <c t="s" r="K114" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5141,7 +5161,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5153,7 +5173,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>71</v>
@@ -5174,7 +5194,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5186,10 +5206,10 @@
         <v>126</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5207,7 +5227,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5222,7 +5242,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5255,7 +5275,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5275,7 +5295,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5290,7 +5310,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5305,7 +5325,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5323,7 +5343,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5335,7 +5355,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>149</v>
@@ -5356,7 +5376,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5371,7 +5391,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5400,17 +5420,17 @@
         <v>7707</v>
       </c>
       <c t="s" r="C124" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>17</v>
@@ -5423,7 +5443,9 @@
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
+      <c t="s" r="M124" s="7">
+        <v>116</v>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c t="s" r="A125" s="6">
@@ -5433,11 +5455,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C125" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5470,7 +5492,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5482,10 +5504,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5503,7 +5525,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5512,13 +5534,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5547,11 +5569,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C129" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5563,15 +5585,15 @@
         <v>142</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5586,7 +5608,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5598,10 +5620,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5619,7 +5641,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5631,7 +5653,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>164</v>
@@ -5652,7 +5674,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5664,10 +5686,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5700,7 +5722,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5712,7 +5734,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>75</v>
@@ -5720,7 +5742,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5731,11 +5753,11 @@
         <v>7658</v>
       </c>
       <c t="s" r="C135" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5747,10 +5769,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5764,11 +5786,11 @@
         <v>7658</v>
       </c>
       <c t="s" r="C136" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5777,13 +5799,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5812,11 +5834,11 @@
         <v>7820</v>
       </c>
       <c t="s" r="C138" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5825,13 +5847,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I138" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5845,23 +5867,23 @@
         <v>7821</v>
       </c>
       <c t="s" r="C139" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>140</v>
@@ -5882,7 +5904,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5894,10 +5916,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5930,7 +5952,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5945,12 +5967,12 @@
         <v>35</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -5965,7 +5987,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5977,10 +5999,10 @@
         <v>142</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5998,7 +6020,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6010,7 +6032,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>148</v>
@@ -6046,7 +6068,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6066,7 +6088,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6081,7 +6103,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6090,13 +6112,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6114,13 +6136,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>17</v>
@@ -6129,7 +6151,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6147,7 +6169,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6156,13 +6178,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I149" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6180,22 +6202,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6228,7 +6250,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6240,7 +6262,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>167</v>
@@ -6248,7 +6270,7 @@
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6263,7 +6285,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6272,7 +6294,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I153" s="7">
         <v>160</v>
@@ -6296,19 +6318,19 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>62</v>
@@ -6329,7 +6351,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6338,13 +6360,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>64</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6362,22 +6384,22 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6410,7 +6432,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6422,10 +6444,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6443,7 +6465,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6455,10 +6477,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6476,7 +6498,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6488,7 +6510,7 @@
         <v>61</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>69</v>
@@ -6509,7 +6531,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6521,10 +6543,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6542,7 +6564,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6575,7 +6597,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6623,7 +6645,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6632,7 +6654,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I165" s="7">
         <v>186</v>
@@ -6643,7 +6665,7 @@
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -6658,19 +6680,19 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>35</v>
@@ -6678,7 +6700,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -6693,7 +6715,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6708,7 +6730,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6726,7 +6748,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6738,10 +6760,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6759,7 +6781,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6768,10 +6790,10 @@
         <v>44</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>99</v>
@@ -6792,22 +6814,22 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6840,7 +6862,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6849,10 +6871,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>111</v>
@@ -6860,7 +6882,7 @@
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -6875,13 +6897,13 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>17</v>
@@ -6908,7 +6930,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6920,7 +6942,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>43</v>
@@ -6941,7 +6963,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6953,10 +6975,10 @@
         <v>104</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6974,7 +6996,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6989,7 +7011,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7007,7 +7029,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7019,10 +7041,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7040,7 +7062,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7052,10 +7074,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7088,7 +7110,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7100,15 +7122,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7123,7 +7145,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7138,7 +7160,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7156,7 +7178,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7168,10 +7190,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7189,7 +7211,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7198,7 +7220,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>177</v>
@@ -7222,13 +7244,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>17</v>
@@ -7255,7 +7277,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7288,7 +7310,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7300,7 +7322,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>28</v>
@@ -7336,7 +7358,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7345,13 +7367,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="I188" s="7">
         <v>158</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7369,22 +7391,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7402,7 +7424,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7411,13 +7433,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I190" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7435,22 +7457,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7468,7 +7490,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7483,7 +7505,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7501,7 +7523,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7513,10 +7535,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7549,7 +7571,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7568,7 +7590,9 @@
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
-      <c r="M195" s="7"/>
+      <c t="s" r="M195" s="7">
+        <v>297</v>
+      </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c t="s" r="A196" s="6">
@@ -7582,7 +7606,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7594,10 +7618,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7608,14 +7632,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B197" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7630,14 +7654,14 @@
         <v>22</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="K197" s="7">
         <v>22</v>
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7652,7 +7676,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7667,7 +7691,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7685,7 +7709,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7697,10 +7721,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7718,7 +7742,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7730,10 +7754,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7766,7 +7790,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7781,12 +7805,12 @@
         <v>108</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7801,7 +7825,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7816,7 +7840,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7834,7 +7858,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7867,7 +7891,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7900,7 +7924,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7933,7 +7957,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7948,7 +7972,7 @@
         <v>178</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7981,7 +8005,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7990,18 +8014,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="I209" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8016,13 +8040,13 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>17</v>
@@ -8031,7 +8055,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8049,7 +8073,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8082,7 +8106,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8130,7 +8154,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8142,10 +8166,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8163,7 +8187,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8211,7 +8235,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8223,10 +8247,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8244,7 +8268,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8292,7 +8316,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8304,15 +8328,15 @@
         <v>104</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8327,7 +8351,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8339,14 +8363,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
-      <c r="M221" s="7"/>
+      <c t="s" r="M221" s="7">
+        <v>313</v>
+      </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
       <c t="s" r="A222" s="6">
@@ -8360,7 +8386,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8369,13 +8395,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I222" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8393,22 +8419,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8426,7 +8452,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8459,7 +8485,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8474,7 +8500,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8507,7 +8533,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8516,7 +8542,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>132</v>
@@ -8540,19 +8566,19 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>71</v>
@@ -8573,7 +8599,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8588,7 +8614,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8606,7 +8632,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8618,7 +8644,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>68</v>
@@ -8654,7 +8680,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8666,15 +8692,15 @@
         <v>126</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -8689,7 +8715,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8701,10 +8727,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8724,7 +8750,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8757,7 +8783,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8772,7 +8798,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8790,7 +8816,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8802,10 +8828,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8823,7 +8849,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8838,7 +8864,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8856,7 +8882,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8865,10 +8891,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>68</v>
@@ -8904,7 +8930,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8916,7 +8942,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>175</v>
@@ -8924,7 +8950,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -8939,7 +8965,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8948,13 +8974,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>167</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8972,13 +8998,13 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>44</v>
@@ -9005,7 +9031,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9014,7 +9040,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="I243" s="7">
         <v>99</v>
@@ -9053,7 +9079,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9073,7 +9099,7 @@
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9088,7 +9114,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9121,7 +9147,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9136,7 +9162,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9154,7 +9180,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9187,7 +9213,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9202,7 +9228,7 @@
         <v>189</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9220,7 +9246,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9253,7 +9279,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9265,7 +9291,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>120</v>
@@ -9301,7 +9327,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9313,10 +9339,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9336,7 +9362,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9351,14 +9377,14 @@
         <v>57</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="K254" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -9373,7 +9399,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9388,7 +9414,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="K255" s="7">
         <v>38</v>
@@ -9410,7 +9436,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9425,7 +9451,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9443,7 +9469,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9455,10 +9481,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9491,7 +9517,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9500,10 +9526,10 @@
         <v>44</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>186</v>
@@ -9511,7 +9537,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -9526,13 +9552,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>44</v>
@@ -9541,12 +9567,12 @@
         <v>84</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9557,11 +9583,11 @@
         <v>37</v>
       </c>
       <c t="s" r="C261" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
@@ -9570,13 +9596,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9590,26 +9616,26 @@
         <v>1875</v>
       </c>
       <c t="s" r="C262" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9623,26 +9649,26 @@
         <v>1876</v>
       </c>
       <c t="s" r="C263" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9675,7 +9701,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9687,7 +9713,7 @@
         <v>126</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>143</v>
@@ -9695,7 +9721,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9710,7 +9736,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9722,15 +9748,15 @@
         <v>44</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -9745,7 +9771,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9757,10 +9783,10 @@
         <v>107</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9778,7 +9804,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9790,7 +9816,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>169</v>
@@ -9811,7 +9837,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9826,7 +9852,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9844,7 +9870,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9856,10 +9882,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9877,7 +9903,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9889,10 +9915,10 @@
         <v>123</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9910,7 +9936,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9922,10 +9948,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9958,7 +9984,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9970,14 +9996,16 @@
         <v>123</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>155</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
-      <c r="M274" s="7"/>
+      <c t="s" r="M274" s="7">
+        <v>352</v>
+      </c>
     </row>
     <row r="275" ht="15" customHeight="1">
       <c t="s" r="A275" s="6">
@@ -9991,7 +10019,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10024,7 +10052,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10036,7 +10064,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>23</v>
@@ -10057,7 +10085,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10090,7 +10118,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10138,7 +10166,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10150,15 +10178,15 @@
         <v>142</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10169,11 +10197,11 @@
         <v>5924</v>
       </c>
       <c t="s" r="C281" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10185,7 +10213,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>134</v>
@@ -10193,7 +10221,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10204,11 +10232,11 @@
         <v>3867</v>
       </c>
       <c t="s" r="C282" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10241,7 +10269,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10274,7 +10302,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10283,10 +10311,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>35</v>
@@ -10322,7 +10350,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10331,18 +10359,18 @@
         <v>44</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>101</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10357,27 +10385,27 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10392,7 +10420,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10404,7 +10432,7 @@
         <v>104</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>167</v>
@@ -10425,7 +10453,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10440,7 +10468,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10458,7 +10486,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10470,7 +10498,7 @@
         <v>137</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>134</v>
@@ -10491,7 +10519,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10506,7 +10534,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10539,7 +10567,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10551,15 +10579,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -10574,7 +10602,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10593,7 +10621,9 @@
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
-      <c r="M294" s="7"/>
+      <c t="s" r="M294" s="7">
+        <v>364</v>
+      </c>
     </row>
     <row r="295" ht="15" customHeight="1">
       <c t="s" r="A295" s="6">
@@ -10607,7 +10637,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10616,7 +10646,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>96</v>
@@ -10640,13 +10670,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>44</v>
@@ -10673,7 +10703,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10682,7 +10712,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="I297" s="7">
         <v>191</v>
@@ -10706,13 +10736,13 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>44</v>
@@ -10754,7 +10784,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10766,7 +10796,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>20</v>
@@ -10787,7 +10817,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10799,7 +10829,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>118</v>
@@ -10820,7 +10850,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10829,13 +10859,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>146</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10853,13 +10883,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>44</v>
@@ -10868,7 +10898,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10886,7 +10916,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10895,10 +10925,10 @@
         <v>44</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>30</v>
@@ -10919,22 +10949,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10967,7 +10997,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10976,7 +11006,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="I307" s="7">
         <v>116</v>
@@ -11000,19 +11030,19 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>46</v>
@@ -11048,7 +11078,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11057,7 +11087,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I310" s="7">
         <v>84</v>
@@ -11068,7 +11098,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11083,13 +11113,13 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>17</v>
@@ -11116,7 +11146,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11128,7 +11158,7 @@
         <v>142</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>153</v>
@@ -11149,7 +11179,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11158,7 +11188,7 @@
         <v>142</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>116</v>
@@ -11182,19 +11212,19 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>142</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>147</v>
@@ -11215,7 +11245,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11230,7 +11260,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11263,7 +11293,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11272,7 +11302,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>158</v>
@@ -11296,22 +11326,22 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11329,7 +11359,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11338,13 +11368,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>134</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11362,13 +11392,13 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>17</v>
@@ -11377,7 +11407,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11410,7 +11440,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11425,12 +11455,12 @@
         <v>125</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11445,7 +11475,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11478,7 +11508,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11493,7 +11523,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11511,7 +11541,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11544,7 +11574,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11577,7 +11607,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11625,7 +11655,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11634,7 +11664,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="I329" s="7">
         <v>35</v>
@@ -11658,13 +11688,13 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>44</v>
@@ -11673,7 +11703,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11691,7 +11721,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11700,13 +11730,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11724,22 +11754,22 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11772,7 +11802,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11781,13 +11811,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c t="s" r="I334" s="7">
         <v>152</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11805,19 +11835,19 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>164</v>
@@ -11838,7 +11868,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11847,13 +11877,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11871,13 +11901,13 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
@@ -11886,7 +11916,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11919,7 +11949,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11928,7 +11958,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>133</v>
@@ -11952,22 +11982,22 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12000,7 +12030,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -12009,18 +12039,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12035,19 +12065,19 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>40</v>
@@ -12068,7 +12098,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -12083,7 +12113,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12101,7 +12131,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12113,7 +12143,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>178</v>
@@ -12134,7 +12164,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12146,7 +12176,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>108</v>
@@ -12182,7 +12212,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12194,7 +12224,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>57</v>
@@ -12202,7 +12232,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12217,7 +12247,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12226,13 +12256,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12250,13 +12280,13 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>44</v>
@@ -12283,7 +12313,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12295,10 +12325,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12316,7 +12346,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12328,10 +12358,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12349,7 +12379,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12364,7 +12394,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12397,7 +12427,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12409,7 +12439,7 @@
         <v>142</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>128</v>
@@ -12417,7 +12447,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -12428,11 +12458,11 @@
         <v>5926</v>
       </c>
       <c t="s" r="C356" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12444,7 +12474,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>43</v>
@@ -12461,11 +12491,11 @@
         <v>8663</v>
       </c>
       <c t="s" r="C357" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12477,7 +12507,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>25</v>
@@ -12513,7 +12543,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12525,15 +12555,15 @@
         <v>104</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -12548,7 +12578,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12568,7 +12598,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -12583,7 +12613,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12598,7 +12628,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12616,7 +12646,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12631,7 +12661,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12649,7 +12679,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12697,7 +12727,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12717,7 +12747,7 @@
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>155</v>
+        <v>57</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -12732,7 +12762,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12744,17 +12774,17 @@
         <v>44</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="K366" s="7">
-        <v>158</v>
+        <v>321</v>
       </c>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>223</v>
+        <v>288</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -12769,7 +12799,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12781,7 +12811,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>117</v>
@@ -12802,7 +12832,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12811,7 +12841,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I368" s="7">
         <v>71</v>
@@ -12835,13 +12865,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>34</v>
@@ -12850,7 +12880,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12868,7 +12898,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12880,10 +12910,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12916,7 +12946,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12928,15 +12958,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -12951,7 +12981,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12984,7 +13014,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12996,10 +13026,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13017,7 +13047,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13029,10 +13059,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13050,7 +13080,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13062,10 +13092,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13098,7 +13128,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13110,7 +13140,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>153</v>
@@ -13131,7 +13161,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13146,7 +13176,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13179,7 +13209,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13199,7 +13229,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13214,7 +13244,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13247,7 +13277,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13280,7 +13310,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13313,7 +13343,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13322,10 +13352,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>183</v>
@@ -13346,22 +13376,22 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13379,7 +13409,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13391,7 +13421,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>84</v>
@@ -13427,7 +13457,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13439,7 +13469,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>95</v>
@@ -13447,7 +13477,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13462,7 +13492,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13481,7 +13511,9 @@
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
-      <c r="M390" s="7"/>
+      <c t="s" r="M390" s="7">
+        <v>312</v>
+      </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
       <c t="s" r="A391" s="6">
@@ -13495,7 +13527,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13510,7 +13542,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13528,7 +13560,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13543,7 +13575,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13561,7 +13593,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13576,7 +13608,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13594,7 +13626,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13642,7 +13674,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13654,10 +13686,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13677,7 +13709,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13689,7 +13721,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>79</v>
@@ -13710,7 +13742,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13719,7 +13751,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>116</v>
@@ -13743,22 +13775,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13776,7 +13808,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13785,7 +13817,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>183</v>
@@ -13809,19 +13841,19 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>124</v>
@@ -13857,7 +13889,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13877,7 +13909,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -13892,7 +13924,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13925,7 +13957,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13934,13 +13966,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13958,22 +13990,22 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14006,7 +14038,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14015,18 +14047,18 @@
         <v>44</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14041,19 +14073,19 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>97</v>
@@ -14074,7 +14106,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14086,7 +14118,7 @@
         <v>104</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>117</v>
@@ -14107,7 +14139,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14140,7 +14172,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14152,10 +14184,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14188,7 +14220,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14200,7 +14232,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>144</v>
@@ -14221,7 +14253,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14254,7 +14286,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14269,7 +14301,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14287,7 +14319,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14320,7 +14352,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14353,7 +14385,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14365,7 +14397,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>92</v>
@@ -14401,7 +14433,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14436,7 +14468,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -14448,10 +14480,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14469,7 +14501,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14481,10 +14513,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14502,7 +14534,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14550,7 +14582,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
@@ -14562,7 +14594,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>132</v>
@@ -14583,7 +14615,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
@@ -14592,13 +14624,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c t="s" r="I427" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14616,22 +14648,22 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14664,22 +14696,22 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>142</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14714,19 +14746,19 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>189</v>
@@ -14734,7 +14766,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -14749,7 +14781,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -14758,10 +14790,10 @@
         <v>44</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>127</v>
@@ -14797,7 +14829,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
@@ -14809,15 +14841,15 @@
         <v>44</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -14832,7 +14864,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -14844,7 +14876,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>151</v>
@@ -14852,7 +14884,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>130</v>
+        <v>434</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -14867,7 +14899,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -14876,7 +14908,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c t="s" r="I437" s="7">
         <v>36</v>
@@ -14900,22 +14932,22 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -14944,26 +14976,26 @@
         <v>2</v>
       </c>
       <c t="s" r="C440" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14996,7 +15028,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
@@ -15005,13 +15037,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15029,19 +15061,19 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>124</v>
@@ -15052,7 +15084,7 @@
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c t="s" r="A444" s="9">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B444" s="9"/>
       <c r="C444" s="9"/>
@@ -15072,7 +15104,7 @@
     <row r="445" ht="66" customHeight="1"/>
     <row r="446" ht="16.5" customHeight="1">
       <c t="s" r="A446" s="10">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B446" s="10"/>
       <c r="C446" s="10"/>
@@ -15085,7 +15117,7 @@
       <c r="J446" s="10"/>
       <c r="K446" s="10"/>
       <c t="s" r="L446" s="11">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="M446" s="11"/>
       <c r="N446" s="11"/>

--- a/Data/FlightPlan/FPL_23SEP26.xlsx
+++ b/Data/FlightPlan/FPL_23SEP26.xlsx
@@ -578,7 +578,7 @@
     <t>11:47</t>
   </si>
   <si>
-    <t>15:04</t>
+    <t>15:10</t>
   </si>
   <si>
     <t>17:20</t>
@@ -647,9 +647,6 @@
     <t>14:40</t>
   </si>
   <si>
-    <t>15:10</t>
-  </si>
-  <si>
     <t>17:00</t>
   </si>
   <si>
@@ -926,7 +923,7 @@
     <t>11:03</t>
   </si>
   <si>
-    <t>13:31</t>
+    <t>13:34</t>
   </si>
   <si>
     <t>431A *</t>
@@ -953,6 +950,9 @@
     <t>11:44</t>
   </si>
   <si>
+    <t>14:46</t>
+  </si>
+  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -983,6 +983,9 @@
     <t>SIN</t>
   </si>
   <si>
+    <t>15:01</t>
+  </si>
+  <si>
     <t>15:25</t>
   </si>
   <si>
@@ -1028,153 +1031,156 @@
     <t>08:52</t>
   </si>
   <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:43</t>
+  </si>
+  <si>
+    <t>08:26</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>MAA</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>02:55</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>09:17</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>09:53</t>
+  </si>
+  <si>
+    <t>11:57</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>07:43</t>
+  </si>
+  <si>
+    <t>15:43</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>07:11</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>12:03</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
     <t>12:45</t>
   </si>
   <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>12:47</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:43</t>
-  </si>
-  <si>
-    <t>08:26</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>MAA</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>02:55</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>07:31</t>
-  </si>
-  <si>
-    <t>09:17</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>11:46</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>09:53</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>07:43</t>
-  </si>
-  <si>
-    <t>15:43</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>07:11</t>
-  </si>
-  <si>
-    <t>10:26</t>
-  </si>
-  <si>
-    <t>12:03</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
     <t>VDH</t>
   </si>
   <si>
@@ -1331,7 +1337,7 @@
     <t>VN-A689</t>
   </si>
   <si>
-    <t>12:58</t>
+    <t>12:59</t>
   </si>
   <si>
     <t>VN-A693</t>
@@ -1358,9 +1364,6 @@
     <t>10:37</t>
   </si>
   <si>
-    <t>12:38</t>
-  </si>
-  <si>
     <t>VN-A699</t>
   </si>
   <si>
@@ -1427,7 +1430,7 @@
     <t>Total Record(s): 360</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 23, 2026 11:29</t>
+    <t xml:space="preserve">Generated on  Sep 23, 2026 11:40</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5358,11 +5361,11 @@
         <v>73</v>
       </c>
       <c t="s" r="K117" s="7">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5389,10 +5392,10 @@
         <v>130</v>
       </c>
       <c t="s" r="I118" s="7">
+        <v>213</v>
+      </c>
+      <c t="s" r="J118" s="7">
         <v>214</v>
-      </c>
-      <c t="s" r="J118" s="7">
-        <v>215</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5425,7 +5428,7 @@
         <v>200</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5458,7 +5461,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5478,7 +5481,7 @@
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5493,7 +5496,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5508,12 +5511,12 @@
         <v>163</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -5528,7 +5531,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5540,7 +5543,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>154</v>
@@ -5561,7 +5564,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5576,7 +5579,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5605,17 +5608,17 @@
         <v>7707</v>
       </c>
       <c t="s" r="C126" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
+        <v>222</v>
+      </c>
+      <c r="F126" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G126" s="8">
         <v>223</v>
-      </c>
-      <c r="F126" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G126" s="8">
-        <v>224</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>17</v>
@@ -5640,11 +5643,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C127" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5677,7 +5680,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5689,10 +5692,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I128" s="7">
+        <v>224</v>
+      </c>
+      <c t="s" r="J128" s="7">
         <v>225</v>
-      </c>
-      <c t="s" r="J128" s="7">
-        <v>226</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5710,7 +5713,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5719,13 +5722,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H129" s="8">
+        <v>226</v>
+      </c>
+      <c t="s" r="I129" s="7">
         <v>227</v>
       </c>
-      <c t="s" r="I129" s="7">
+      <c t="s" r="J129" s="7">
         <v>228</v>
-      </c>
-      <c t="s" r="J129" s="7">
-        <v>229</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5754,11 +5757,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C131" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5770,15 +5773,15 @@
         <v>147</v>
       </c>
       <c t="s" r="I131" s="7">
+        <v>230</v>
+      </c>
+      <c t="s" r="J131" s="7">
         <v>231</v>
-      </c>
-      <c t="s" r="J131" s="7">
-        <v>232</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -5793,7 +5796,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5805,15 +5808,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I132" s="7">
+        <v>233</v>
+      </c>
+      <c t="s" r="J132" s="7">
         <v>234</v>
-      </c>
-      <c t="s" r="J132" s="7">
-        <v>235</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -5828,7 +5831,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5840,10 +5843,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I133" s="7">
+        <v>236</v>
+      </c>
+      <c t="s" r="J133" s="7">
         <v>237</v>
-      </c>
-      <c t="s" r="J133" s="7">
-        <v>238</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5861,7 +5864,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5873,10 +5876,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I134" s="7">
+        <v>238</v>
+      </c>
+      <c t="s" r="J134" s="7">
         <v>239</v>
-      </c>
-      <c t="s" r="J134" s="7">
-        <v>240</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5909,7 +5912,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5921,7 +5924,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>77</v>
@@ -5929,7 +5932,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -5940,11 +5943,11 @@
         <v>7658</v>
       </c>
       <c t="s" r="C137" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5959,7 +5962,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5973,11 +5976,11 @@
         <v>7658</v>
       </c>
       <c t="s" r="C138" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5986,13 +5989,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H138" s="8">
+        <v>244</v>
+      </c>
+      <c t="s" r="I138" s="7">
         <v>245</v>
       </c>
-      <c t="s" r="I138" s="7">
+      <c t="s" r="J138" s="7">
         <v>246</v>
-      </c>
-      <c t="s" r="J138" s="7">
-        <v>247</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6021,11 +6024,11 @@
         <v>7820</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6034,18 +6037,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>134</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6056,23 +6059,23 @@
         <v>7821</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
+        <v>247</v>
+      </c>
+      <c r="F141" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G141" s="8">
         <v>248</v>
-      </c>
-      <c r="F141" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G141" s="8">
-        <v>249</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>95</v>
@@ -6093,7 +6096,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6108,7 +6111,7 @@
         <v>193</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6141,7 +6144,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6156,12 +6159,12 @@
         <v>35</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6176,7 +6179,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6191,7 +6194,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6209,7 +6212,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6221,10 +6224,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I146" s="7">
+        <v>254</v>
+      </c>
+      <c t="s" r="J146" s="7">
         <v>255</v>
-      </c>
-      <c t="s" r="J146" s="7">
-        <v>256</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6257,7 +6260,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6292,7 +6295,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6301,13 +6304,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
+        <v>257</v>
+      </c>
+      <c t="s" r="I149" s="7">
         <v>258</v>
       </c>
-      <c t="s" r="I149" s="7">
-        <v>259</v>
-      </c>
       <c t="s" r="J149" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6325,13 +6328,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
+        <v>256</v>
+      </c>
+      <c r="F150" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G150" s="8">
         <v>257</v>
-      </c>
-      <c r="F150" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G150" s="8">
-        <v>258</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>17</v>
@@ -6358,7 +6361,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6367,13 +6370,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c t="s" r="I151" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6391,22 +6394,22 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I152" s="7">
+        <v>261</v>
+      </c>
+      <c t="s" r="J152" s="7">
         <v>262</v>
-      </c>
-      <c t="s" r="J152" s="7">
-        <v>263</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6439,7 +6442,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6451,7 +6454,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>172</v>
@@ -6459,7 +6462,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6474,7 +6477,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6483,7 +6486,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>165</v>
@@ -6507,13 +6510,13 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>33</v>
@@ -6540,7 +6543,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6549,13 +6552,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c t="s" r="I157" s="7">
         <v>66</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6573,22 +6576,22 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I158" s="7">
+        <v>267</v>
+      </c>
+      <c t="s" r="J158" s="7">
         <v>268</v>
-      </c>
-      <c t="s" r="J158" s="7">
-        <v>269</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6621,7 +6624,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6633,15 +6636,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I160" s="7">
+        <v>270</v>
+      </c>
+      <c t="s" r="J160" s="7">
         <v>271</v>
-      </c>
-      <c t="s" r="J160" s="7">
-        <v>272</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -6656,7 +6659,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6668,10 +6671,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6689,7 +6692,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6722,7 +6725,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6734,10 +6737,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I163" s="7">
+        <v>273</v>
+      </c>
+      <c t="s" r="J163" s="7">
         <v>274</v>
-      </c>
-      <c t="s" r="J163" s="7">
-        <v>275</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6755,7 +6758,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6803,19 +6806,19 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
+        <v>275</v>
+      </c>
+      <c r="F166" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G166" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="H166" s="8">
         <v>276</v>
       </c>
-      <c r="F166" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G166" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="H166" s="8">
-        <v>277</v>
-      </c>
       <c t="s" r="I166" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>77</v>
@@ -6823,7 +6826,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -6838,19 +6841,19 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
+        <v>275</v>
+      </c>
+      <c r="F167" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G167" s="8">
         <v>276</v>
       </c>
-      <c r="F167" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G167" s="8">
-        <v>277</v>
-      </c>
       <c t="s" r="H167" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>35</v>
@@ -6858,7 +6861,7 @@
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -6873,7 +6876,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6906,7 +6909,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6939,7 +6942,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6948,10 +6951,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>102</v>
@@ -6972,22 +6975,22 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I171" s="7">
+        <v>281</v>
+      </c>
+      <c t="s" r="J171" s="7">
         <v>282</v>
-      </c>
-      <c t="s" r="J171" s="7">
-        <v>283</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7020,7 +7023,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7032,7 +7035,7 @@
         <v>166</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>114</v>
@@ -7040,7 +7043,7 @@
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7055,7 +7058,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7075,7 +7078,7 @@
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7090,7 +7093,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7123,7 +7126,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7138,7 +7141,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7156,7 +7159,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7168,10 +7171,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7189,7 +7192,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7201,10 +7204,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7222,7 +7225,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7234,10 +7237,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I179" s="7">
+        <v>288</v>
+      </c>
+      <c t="s" r="J179" s="7">
         <v>289</v>
-      </c>
-      <c t="s" r="J179" s="7">
-        <v>290</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7270,7 +7273,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7282,15 +7285,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7305,7 +7308,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7320,7 +7323,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7340,7 +7343,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7352,10 +7355,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I183" s="7">
+        <v>293</v>
+      </c>
+      <c t="s" r="J183" s="7">
         <v>294</v>
-      </c>
-      <c t="s" r="J183" s="7">
-        <v>295</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7373,7 +7376,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7382,7 +7385,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>183</v>
@@ -7406,13 +7409,13 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>17</v>
@@ -7454,27 +7457,27 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
+        <v>295</v>
+      </c>
+      <c r="F187" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G187" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="H187" s="8">
         <v>296</v>
-      </c>
-      <c r="F187" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G187" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="H187" s="8">
-        <v>297</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>163</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7489,22 +7492,22 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
+        <v>295</v>
+      </c>
+      <c r="F188" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G188" s="8">
         <v>296</v>
       </c>
-      <c r="F188" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G188" s="8">
-        <v>297</v>
-      </c>
       <c t="s" r="H188" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I188" s="7">
+        <v>298</v>
+      </c>
+      <c t="s" r="J188" s="7">
         <v>299</v>
-      </c>
-      <c t="s" r="J188" s="7">
-        <v>300</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7522,7 +7525,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7531,7 +7534,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>122</v>
@@ -7555,22 +7558,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7588,7 +7591,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7603,7 +7606,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7621,7 +7624,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7633,10 +7636,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7669,7 +7672,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7689,7 +7692,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7704,7 +7707,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7719,12 +7722,12 @@
         <v>195</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -7732,14 +7735,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B196" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7754,14 +7757,14 @@
         <v>22</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c t="s" r="K196" s="7">
         <v>22</v>
       </c>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -7776,7 +7779,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7809,7 +7812,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7821,10 +7824,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I198" s="7">
+        <v>238</v>
+      </c>
+      <c t="s" r="J198" s="7">
         <v>239</v>
-      </c>
-      <c t="s" r="J198" s="7">
-        <v>240</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7842,7 +7845,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7854,10 +7857,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7890,7 +7893,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7905,12 +7908,12 @@
         <v>111</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -7925,7 +7928,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7940,7 +7943,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7960,7 +7963,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7993,7 +7996,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8026,7 +8029,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8059,7 +8062,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8074,7 +8077,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8107,7 +8110,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8116,18 +8119,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="I208" s="7">
         <v>113</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8142,13 +8145,13 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>17</v>
@@ -8161,7 +8164,9 @@
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
-      <c r="M209" s="7"/>
+      <c t="s" r="M209" s="7">
+        <v>313</v>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c t="s" r="A210" s="6">
@@ -8175,7 +8180,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8208,7 +8213,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8268,7 +8273,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>106</v>
@@ -8276,7 +8281,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8351,10 +8356,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8432,7 +8437,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>317</v>
@@ -8440,7 +8445,7 @@
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8475,7 +8480,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8505,14 +8510,14 @@
         <v>40</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c t="s" r="K221" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>120</v>
+        <v>298</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8572,7 +8577,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>321</v>
@@ -8627,7 +8632,9 @@
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
-      <c r="M225" s="7"/>
+      <c t="s" r="M225" s="7">
+        <v>324</v>
+      </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c t="s" r="A226" s="6">
@@ -8653,7 +8660,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>73</v>
@@ -8722,7 +8729,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8755,7 +8762,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8770,12 +8777,12 @@
         <v>208</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -8790,7 +8797,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8802,10 +8809,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8825,7 +8832,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8845,7 +8852,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -8860,7 +8867,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8893,7 +8900,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8905,10 +8912,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8926,7 +8933,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8941,7 +8948,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8959,7 +8966,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8968,10 +8975,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>70</v>
@@ -9007,7 +9014,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9027,7 +9034,7 @@
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9042,7 +9049,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9051,18 +9058,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="I239" s="7">
         <v>172</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9077,13 +9084,13 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>46</v>
@@ -9110,7 +9117,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9119,7 +9126,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>102</v>
@@ -9158,7 +9165,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9178,7 +9185,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9193,7 +9200,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9213,7 +9220,7 @@
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9228,7 +9235,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9243,12 +9250,12 @@
         <v>137</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9263,7 +9270,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9275,7 +9282,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>71</v>
@@ -9296,7 +9303,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9329,7 +9336,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9362,7 +9369,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9374,7 +9381,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>124</v>
@@ -9410,7 +9417,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9422,7 +9429,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>318</v>
@@ -9445,7 +9452,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9460,14 +9467,14 @@
         <v>58</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="K252" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -9482,7 +9489,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9494,10 +9501,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9515,7 +9522,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9527,10 +9534,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9548,7 +9555,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9596,7 +9603,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9605,18 +9612,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9631,13 +9638,13 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>46</v>
@@ -9646,12 +9653,12 @@
         <v>87</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -9662,11 +9669,11 @@
         <v>37</v>
       </c>
       <c t="s" r="C259" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9675,13 +9682,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9695,26 +9702,26 @@
         <v>1875</v>
       </c>
       <c t="s" r="C260" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="I260" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9728,26 +9735,26 @@
         <v>1876</v>
       </c>
       <c t="s" r="C261" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9780,7 +9787,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9792,7 +9799,7 @@
         <v>130</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>148</v>
@@ -9800,7 +9807,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -9815,7 +9822,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9827,15 +9834,15 @@
         <v>46</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -9850,7 +9857,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9862,15 +9869,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9885,7 +9892,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9897,7 +9904,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>175</v>
@@ -9918,7 +9925,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9951,7 +9958,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9963,10 +9970,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9984,7 +9991,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9996,10 +10003,10 @@
         <v>127</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -10017,7 +10024,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10029,10 +10036,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10065,7 +10072,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10077,7 +10084,7 @@
         <v>127</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>160</v>
@@ -10085,7 +10092,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10100,7 +10107,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10120,7 +10127,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10135,7 +10142,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10147,7 +10154,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>23</v>
@@ -10168,7 +10175,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10183,7 +10190,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10201,7 +10208,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10249,7 +10256,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10261,15 +10268,15 @@
         <v>147</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10280,11 +10287,11 @@
         <v>5924</v>
       </c>
       <c t="s" r="C279" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10304,7 +10311,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10315,11 +10322,11 @@
         <v>3867</v>
       </c>
       <c t="s" r="C280" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10352,7 +10359,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10364,7 +10371,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>28</v>
@@ -10385,7 +10392,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10394,10 +10401,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>35</v>
@@ -10433,7 +10440,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10448,12 +10455,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10468,7 +10475,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10480,15 +10487,15 @@
         <v>46</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10503,7 +10510,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10523,7 +10530,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10538,7 +10545,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10553,12 +10560,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10573,7 +10580,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10606,7 +10613,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10654,7 +10661,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10666,15 +10673,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -10689,7 +10696,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10724,7 +10731,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10733,7 +10740,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>99</v>
@@ -10757,13 +10764,13 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>46</v>
@@ -10790,7 +10797,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10799,7 +10806,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>320</v>
@@ -10823,19 +10830,19 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>128</v>
@@ -10871,7 +10878,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10883,7 +10890,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>20</v>
@@ -10891,7 +10898,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>339</v>
+        <v>389</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -10906,7 +10913,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10918,7 +10925,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>122</v>
@@ -10939,7 +10946,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10948,13 +10955,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10972,13 +10979,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>46</v>
@@ -10987,7 +10994,7 @@
         <v>200</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11005,7 +11012,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11014,10 +11021,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>30</v>
@@ -11038,22 +11045,22 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -11086,7 +11093,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11095,7 +11102,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>120</v>
@@ -11119,19 +11126,19 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>48</v>
@@ -11167,7 +11174,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11176,7 +11183,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>87</v>
@@ -11187,7 +11194,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11202,13 +11209,13 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>17</v>
@@ -11237,7 +11244,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11249,7 +11256,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>158</v>
@@ -11270,7 +11277,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11279,7 +11286,7 @@
         <v>147</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>120</v>
@@ -11303,19 +11310,19 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>147</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>152</v>
@@ -11336,7 +11343,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11351,7 +11358,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11384,7 +11391,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11404,7 +11411,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11419,7 +11426,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11431,7 +11438,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>210</v>
@@ -11452,7 +11459,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11467,7 +11474,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11485,7 +11492,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11533,7 +11540,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11548,12 +11555,12 @@
         <v>129</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11568,7 +11575,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11588,7 +11595,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>339</v>
+        <v>389</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11603,7 +11610,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11618,7 +11625,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11636,7 +11643,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11669,7 +11676,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11684,7 +11691,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11702,7 +11709,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11750,7 +11757,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11759,7 +11766,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>35</v>
@@ -11770,7 +11777,7 @@
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -11785,13 +11792,13 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>46</v>
@@ -11818,7 +11825,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11827,13 +11834,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11851,13 +11858,13 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>46</v>
@@ -11866,7 +11873,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11899,7 +11906,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11908,13 +11915,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="I332" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11932,22 +11939,22 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11965,7 +11972,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11974,13 +11981,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11998,13 +12005,13 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>17</v>
@@ -12013,7 +12020,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12046,7 +12053,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12079,7 +12086,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12094,7 +12101,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12127,7 +12134,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12136,18 +12143,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12162,19 +12169,19 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>42</v>
@@ -12182,7 +12189,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12197,7 +12204,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -12230,7 +12237,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -12242,7 +12249,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>184</v>
@@ -12263,7 +12270,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -12275,7 +12282,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>111</v>
@@ -12311,7 +12318,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12323,7 +12330,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>58</v>
@@ -12331,7 +12338,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12346,7 +12353,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12361,7 +12368,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12379,7 +12386,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12412,7 +12419,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12424,10 +12431,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12445,7 +12452,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12457,10 +12464,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12478,7 +12485,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12493,7 +12500,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12526,7 +12533,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12538,7 +12545,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>132</v>
@@ -12546,7 +12553,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12557,11 +12564,11 @@
         <v>5926</v>
       </c>
       <c t="s" r="C354" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12573,7 +12580,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>45</v>
@@ -12581,7 +12588,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12592,11 +12599,11 @@
         <v>8663</v>
       </c>
       <c t="s" r="C355" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12644,7 +12651,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12656,15 +12663,15 @@
         <v>107</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -12679,7 +12686,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12699,7 +12706,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -12714,7 +12721,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12729,12 +12736,12 @@
         <v>116</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -12749,7 +12756,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12764,7 +12771,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12782,7 +12789,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12794,7 +12801,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>199</v>
@@ -12830,7 +12837,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12865,7 +12872,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12877,17 +12884,17 @@
         <v>46</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c t="s" r="K364" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -12902,7 +12909,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12914,7 +12921,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>121</v>
@@ -12935,7 +12942,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12968,7 +12975,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12983,7 +12990,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13001,7 +13008,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13013,10 +13020,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13049,7 +13056,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13061,15 +13068,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13084,7 +13091,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13117,7 +13124,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13150,7 +13157,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13162,10 +13169,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13183,7 +13190,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13195,10 +13202,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13231,7 +13238,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13243,7 +13250,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>158</v>
@@ -13251,7 +13258,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13266,7 +13273,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13278,7 +13285,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>191</v>
@@ -13299,7 +13306,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13311,7 +13318,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>153</v>
@@ -13332,7 +13339,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13344,7 +13351,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>207</v>
@@ -13380,7 +13387,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13400,7 +13407,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13415,7 +13422,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13450,7 +13457,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13468,11 +13475,11 @@
         <v>20</v>
       </c>
       <c t="s" r="K383" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13487,7 +13494,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13505,7 +13512,7 @@
         <v>120</v>
       </c>
       <c t="s" r="K384" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
@@ -13524,7 +13531,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13533,7 +13540,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="I385" s="7">
         <v>168</v>
@@ -13557,22 +13564,22 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13590,7 +13597,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13602,7 +13609,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>87</v>
@@ -13638,7 +13645,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13650,7 +13657,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>98</v>
@@ -13658,7 +13665,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13673,7 +13680,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13693,7 +13700,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13708,7 +13715,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13723,7 +13730,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13741,7 +13748,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13753,10 +13760,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13774,7 +13781,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13786,10 +13793,10 @@
         <v>107</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13807,7 +13814,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13822,7 +13829,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13855,7 +13862,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13870,7 +13877,7 @@
         <v>317</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13890,7 +13897,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13902,7 +13909,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>81</v>
@@ -13910,7 +13917,7 @@
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -13925,7 +13932,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13958,7 +13965,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13970,10 +13977,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13991,7 +13998,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -14000,7 +14007,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>199</v>
@@ -14024,13 +14031,13 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>46</v>
@@ -14072,7 +14079,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14092,7 +14099,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14107,7 +14114,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14140,7 +14147,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14149,13 +14156,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14173,22 +14180,22 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14221,7 +14228,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14236,12 +14243,12 @@
         <v>87</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14256,7 +14263,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14276,7 +14283,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14291,7 +14298,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14303,7 +14310,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>121</v>
@@ -14324,7 +14331,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14357,7 +14364,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14369,7 +14376,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>208</v>
@@ -14405,7 +14412,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14417,7 +14424,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>149</v>
@@ -14425,7 +14432,7 @@
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -14440,7 +14447,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14460,7 +14467,7 @@
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>449</v>
+        <v>423</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -14475,7 +14482,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14508,7 +14515,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14541,7 +14548,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14574,7 +14581,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14586,10 +14593,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14622,7 +14629,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14657,7 +14664,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -14669,10 +14676,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14692,7 +14699,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14704,7 +14711,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>168</v>
@@ -14725,7 +14732,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14773,7 +14780,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
@@ -14785,7 +14792,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>137</v>
@@ -14793,7 +14800,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -14808,7 +14815,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
@@ -14817,7 +14824,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c t="s" r="I427" s="7">
         <v>43</v>
@@ -14841,13 +14848,13 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>33</v>
@@ -14856,7 +14863,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14889,19 +14896,19 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>147</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="J430" s="7">
         <v>211</v>
@@ -14939,19 +14946,19 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>197</v>
@@ -14959,7 +14966,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -14974,7 +14981,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -14983,10 +14990,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>131</v>
@@ -15022,7 +15029,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
@@ -15034,15 +15041,15 @@
         <v>46</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -15057,7 +15064,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -15069,7 +15076,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>156</v>
@@ -15077,7 +15084,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15092,7 +15099,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -15101,7 +15108,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c t="s" r="I437" s="7">
         <v>36</v>
@@ -15112,7 +15119,7 @@
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15127,22 +15134,22 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15171,26 +15178,26 @@
         <v>2</v>
       </c>
       <c t="s" r="C440" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -15223,7 +15230,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
@@ -15232,18 +15239,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -15258,19 +15265,19 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>128</v>
@@ -15281,7 +15288,7 @@
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c t="s" r="A444" s="9">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B444" s="9"/>
       <c r="C444" s="9"/>
@@ -15301,7 +15308,7 @@
     <row r="445" ht="66" customHeight="1"/>
     <row r="446" ht="16.5" customHeight="1">
       <c t="s" r="A446" s="10">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B446" s="10"/>
       <c r="C446" s="10"/>
@@ -15314,7 +15321,7 @@
       <c r="J446" s="10"/>
       <c r="K446" s="10"/>
       <c t="s" r="L446" s="11">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M446" s="11"/>
       <c r="N446" s="11"/>
